--- a/experiment_results/wedos_grid/rtt_bursts_S1_atk10pct_wu350000_stage1b_rep2.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S1_atk10pct_wu350000_stage1b_rep2.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
